--- a/03_RTM/RTM_Matrix_AutomationExercise.xlsx
+++ b/03_RTM/RTM_Matrix_AutomationExercise.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\ktpm\manual_testing\03_RTM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D126A64-A66C-440C-ACB2-F3566CD0705F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,15 +24,120 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+  <si>
+    <t>Covered</t>
+  </si>
+  <si>
+    <t>Trạng thái</t>
+  </si>
+  <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>Mô tả yêu cầu</t>
+  </si>
+  <si>
+    <t>Requirement ID</t>
+  </si>
+  <si>
+    <t>R_PC_01</t>
+  </si>
+  <si>
+    <t>Tìm kiếm sản phẩm linh hoạt (đúng/sai/đặc biệt)</t>
+  </si>
+  <si>
+    <t>R_PC_02</t>
+  </si>
+  <si>
+    <t>Xử lý dữ liệu đầu vào ô số lượng (Số lượng âm/0)</t>
+  </si>
+  <si>
+    <t>R_PC_03</t>
+  </si>
+  <si>
+    <t>Giới hạn số lượng sản phẩm đặt hàng (Biên lớn)</t>
+  </si>
+  <si>
+    <t>R_PC_04</t>
+  </si>
+  <si>
+    <t>Kiểm tra Validation định dạng dữ liệu (Chữ/Ký tự)</t>
+  </si>
+  <si>
+    <t>R_PC_05</t>
+  </si>
+  <si>
+    <t>Quản lý giỏ hàng (Xóa SP/Giỏ hàng trống)</t>
+  </si>
+  <si>
+    <t>R_PC_06</t>
+  </si>
+  <si>
+    <t>Bảo mật giao diện nhập liệu (XSS/SQLi)</t>
+  </si>
+  <si>
+    <t>R_PC_07</t>
+  </si>
+  <si>
+    <t>Chỉnh sửa và cập nhật dữ liệu trong giỏ hàng</t>
+  </si>
+  <si>
+    <t>R_PC_08</t>
+  </si>
+  <si>
+    <t>Điều hướng và luồng thanh toán hợp lệ</t>
+  </si>
+  <si>
+    <t>TC_PRODUCT_001, TC_PRODUCT_002, TC_PRODUCT_003</t>
+  </si>
+  <si>
+    <t>TC_CART_004, TC_CART_005</t>
+  </si>
+  <si>
+    <t>TC_CART_006, TC_CART_014</t>
+  </si>
+  <si>
+    <t>TC_CART_007, TC_PRODUCT_019</t>
+  </si>
+  <si>
+    <t>TC_CART_009, TC_CART_010</t>
+  </si>
+  <si>
+    <t>TC_PRODUCT_011, TC_PRODUCT_018</t>
+  </si>
+  <si>
+    <t>TC_CART_012, TC_CART_013</t>
+  </si>
+  <si>
+    <t>TC_CART_016, TC_CART_020</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +148,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +156,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +462,143 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="54.109375" customWidth="1"/>
+    <col min="3" max="3" width="47.6640625" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="23.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="32.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/03_RTM/RTM_Matrix_AutomationExercise.xlsx
+++ b/03_RTM/RTM_Matrix_AutomationExercise.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\ktpm\manual_testing\03_RTM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D126A64-A66C-440C-ACB2-F3566CD0705F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6C1930-3425-468C-9B1F-E2E2660BDAFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
   <si>
     <t>Covered</t>
   </si>
@@ -42,83 +42,65 @@
     <t>Requirement ID</t>
   </si>
   <si>
-    <t>R_PC_01</t>
-  </si>
-  <si>
-    <t>Tìm kiếm sản phẩm linh hoạt (đúng/sai/đặc biệt)</t>
-  </si>
-  <si>
-    <t>R_PC_02</t>
-  </si>
-  <si>
-    <t>Xử lý dữ liệu đầu vào ô số lượng (Số lượng âm/0)</t>
-  </si>
-  <si>
-    <t>R_PC_03</t>
-  </si>
-  <si>
-    <t>Giới hạn số lượng sản phẩm đặt hàng (Biên lớn)</t>
-  </si>
-  <si>
-    <t>R_PC_04</t>
-  </si>
-  <si>
-    <t>Kiểm tra Validation định dạng dữ liệu (Chữ/Ký tự)</t>
-  </si>
-  <si>
-    <t>R_PC_05</t>
-  </si>
-  <si>
-    <t>Quản lý giỏ hàng (Xóa SP/Giỏ hàng trống)</t>
-  </si>
-  <si>
-    <t>R_PC_06</t>
-  </si>
-  <si>
-    <t>Bảo mật giao diện nhập liệu (XSS/SQLi)</t>
-  </si>
-  <si>
-    <t>R_PC_07</t>
-  </si>
-  <si>
-    <t>Chỉnh sửa và cập nhật dữ liệu trong giỏ hàng</t>
-  </si>
-  <si>
-    <t>R_PC_08</t>
-  </si>
-  <si>
-    <t>Điều hướng và luồng thanh toán hợp lệ</t>
-  </si>
-  <si>
-    <t>TC_PRODUCT_001, TC_PRODUCT_002, TC_PRODUCT_003</t>
-  </si>
-  <si>
-    <t>TC_CART_004, TC_CART_005</t>
-  </si>
-  <si>
-    <t>TC_CART_006, TC_CART_014</t>
-  </si>
-  <si>
-    <t>TC_CART_007, TC_PRODUCT_019</t>
-  </si>
-  <si>
-    <t>TC_CART_009, TC_CART_010</t>
-  </si>
-  <si>
-    <t>TC_PRODUCT_011, TC_PRODUCT_018</t>
-  </si>
-  <si>
-    <t>TC_CART_012, TC_CART_013</t>
-  </si>
-  <si>
-    <t>TC_CART_016, TC_CART_020</t>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>Tìm kiếm hiển thị đúng kết quả</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t>Xem chi tiết sản phẩm</t>
+  </si>
+  <si>
+    <t>TC_CART_004, TC_CART_005, TC_CART_006, TC_CART_007, TC_CART_017, TC_PRODUCT_019</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>Thêm sản phẩm vào giỏ thành công</t>
+  </si>
+  <si>
+    <t>TC_CART_008, TC_CART_014, TC_CART_020</t>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>Cập nhật số lượng trong giỏ</t>
+  </si>
+  <si>
+    <t>TC_CART_004, TC_CART_005, TC_CART_006, TC_CART_012, TC_CART_017</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>Xoá sản phẩm khỏi giỏ</t>
+  </si>
+  <si>
+    <t>TC_CART_009</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>Lọc theo giá hoạt động đúng</t>
+  </si>
+  <si>
+    <t>TC_PRODUCT_021</t>
+  </si>
+  <si>
+    <t>TC_PRODUCT_001, TC_PRODUCT_002, TC_PRODUCT_003, TC_PRODUCT_010, TC_PRODUCT_015, TC_PRODUCT_011, TC_PRODUCT_018</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -127,17 +109,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -157,17 +134,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -175,14 +152,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -463,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -472,129 +450,101 @@
     <col min="4" max="4" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+    <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="25.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="23.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="32.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/03_RTM/RTM_Matrix_AutomationExercise.xlsx
+++ b/03_RTM/RTM_Matrix_AutomationExercise.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VTC\Desktop\manual_testing\03_RTM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E09214-52A1-4B41-BF9F-1BB4F8F6CFF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="0a8ewIeOxbVq6+JjlYQtpwFW8i7AbZxL3n0rfoK7vF4="/>
@@ -16,14 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="110">
   <si>
     <t>Requirement ID</t>
   </si>
   <si>
-    <t xml:space="preserve">Mô tả </t>
-  </si>
-  <si>
     <t>Module chức năng</t>
   </si>
   <si>
@@ -36,9 +42,6 @@
     <t>R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Đăng ký bằng email hợp lệ </t>
-  </si>
-  <si>
     <t>Đăng ký / Đăng nhập</t>
   </si>
   <si>
@@ -51,9 +54,6 @@
     <t>R2</t>
   </si>
   <si>
-    <t xml:space="preserve">Không cho đăng ký khi email sai định dạng </t>
-  </si>
-  <si>
     <t>TC_REG_003, TC_REG_004</t>
   </si>
   <si>
@@ -69,18 +69,12 @@
     <t>R4</t>
   </si>
   <si>
-    <t xml:space="preserve">Đăng nhập thành công với thông tin hợp lệ </t>
-  </si>
-  <si>
     <t>TC_AUTH_001, TC_AUTH_002, TC_AUTH_007, TC_AUTH_008</t>
   </si>
   <si>
     <t>R5</t>
   </si>
   <si>
-    <t xml:space="preserve">Đăng nhập thất bại khi sai mật khẩu </t>
-  </si>
-  <si>
     <t>TC_AUTH_003, TC_AUTH_004</t>
   </si>
   <si>
@@ -96,9 +90,6 @@
     <t>R7</t>
   </si>
   <si>
-    <t xml:space="preserve">Tìm kiếm hiển thị đúng kết quả </t>
-  </si>
-  <si>
     <t>Sản phẩm</t>
   </si>
   <si>
@@ -108,27 +99,18 @@
     <t>R8</t>
   </si>
   <si>
-    <t xml:space="preserve">Lọc theo giá hoạt động đúng </t>
-  </si>
-  <si>
     <t>TC_PROD_003, TC_PROD_004</t>
   </si>
   <si>
     <t>R9</t>
   </si>
   <si>
-    <t xml:space="preserve">Xem chi tiết sản phẩm </t>
-  </si>
-  <si>
     <t>TC_PROD_005, TC_PROD_006</t>
   </si>
   <si>
     <t>R10</t>
   </si>
   <si>
-    <t xml:space="preserve">Thêm sản phẩm vào giỏ thành công </t>
-  </si>
-  <si>
     <t>Sản phẩm / Giỏ hàng</t>
   </si>
   <si>
@@ -150,18 +132,12 @@
     <t>R12</t>
   </si>
   <si>
-    <t xml:space="preserve">Xoá sản phẩm khỏi giỏ </t>
-  </si>
-  <si>
     <t>TC_CART_005, TC_CART_006</t>
   </si>
   <si>
     <t>R13</t>
   </si>
   <si>
-    <t xml:space="preserve">Thanh toán bắt buộc nhập địa chỉ </t>
-  </si>
-  <si>
     <t>Thanh toán</t>
   </si>
   <si>
@@ -171,27 +147,18 @@
     <t>R14</t>
   </si>
   <si>
-    <t xml:space="preserve">Chọn phương thức thanh toán </t>
-  </si>
-  <si>
     <t>TC_CHKT_003, TC_CHKT_004</t>
   </si>
   <si>
     <t>R15</t>
   </si>
   <si>
-    <t xml:space="preserve">Đặt hàng thành công </t>
-  </si>
-  <si>
     <t>TC_CHKT_005, TC_CHKT_006, TC_CHKT_008, TC_CHKT_009</t>
   </si>
   <si>
     <t>R16</t>
   </si>
   <si>
-    <t xml:space="preserve">Lưu lịch sử đơn hàng </t>
-  </si>
-  <si>
     <t>Tài khoản / Đơn hàng</t>
   </si>
   <si>
@@ -313,48 +280,137 @@
   </si>
   <si>
     <t>TC25, TC26</t>
+  </si>
+  <si>
+    <t>Mô tả</t>
+  </si>
+  <si>
+    <t>Đăng ký bằng email hợp lệ</t>
+  </si>
+  <si>
+    <t>Không cho đăng ký khi email sai định dạng</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công với thông tin hợp lệ</t>
+  </si>
+  <si>
+    <t>Đăng nhập thất bại khi sai mật khẩu</t>
+  </si>
+  <si>
+    <t>Tìm kiếm hiển thị đúng kết quả</t>
+  </si>
+  <si>
+    <t>Lọc theo giá hoạt động đúng</t>
+  </si>
+  <si>
+    <t>Xem chi tiết sản phẩm</t>
+  </si>
+  <si>
+    <t>Thêm sản phẩm vào giỏ thành công</t>
+  </si>
+  <si>
+    <t>Xoá sản phẩm khỏi giỏ</t>
+  </si>
+  <si>
+    <t>Thanh toán bắt buộc nhập địa chỉ</t>
+  </si>
+  <si>
+    <t>Chọn phương thức thanh toán</t>
+  </si>
+  <si>
+    <t>Đặt hàng thành công</t>
+  </si>
+  <si>
+    <t>Lưu lịch sử đơn hàng</t>
+  </si>
+  <si>
+    <t>Kết quả</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>BUG_AUTH_001</t>
+  </si>
+  <si>
+    <t>BUG_PROD_001, BUG_PROD_002</t>
+  </si>
+  <si>
+    <t>BUG_CART_001, BUG_CART_002</t>
+  </si>
+  <si>
+    <t>BUG_CART_003, BUG_CART_004</t>
+  </si>
+  <si>
+    <t>BUG_CART_005</t>
+  </si>
+  <si>
+    <t>BUG_CHKT_001, BUG_CHKT_002</t>
+  </si>
+  <si>
+    <t>BUG_CHKT_003</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="&quot;Google Sans Text&quot;"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF1F1F1F"/>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF1F1F1F"/>
-      <name val="&quot;Google Sans Text&quot;"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="20.0"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -362,11 +418,17 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
-    <border/>
+  <borders count="6">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -380,48 +442,113 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -611,701 +738,770 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J1000"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.29"/>
-    <col customWidth="1" min="2" max="2" width="48.14"/>
-    <col customWidth="1" min="3" max="3" width="27.29"/>
-    <col customWidth="1" min="4" max="4" width="35.14"/>
-    <col customWidth="1" min="5" max="5" width="16.71"/>
-    <col customWidth="1" min="6" max="26" width="8.71"/>
+    <col min="1" max="1" width="17.33203125" customWidth="1"/>
+    <col min="2" max="2" width="48.109375" customWidth="1"/>
+    <col min="3" max="3" width="27.33203125" customWidth="1"/>
+    <col min="4" max="4" width="35.109375" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" customWidth="1"/>
+    <col min="7" max="7" width="15.44140625" customWidth="1"/>
+    <col min="8" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-    </row>
-    <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="D2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G2" s="9"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="1:10" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="B3" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-    </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="1" t="s">
+      <c r="E3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3" s="9"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+    </row>
+    <row r="4" spans="1:10" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="C4" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="1" t="s">
+      <c r="E4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G4" s="9"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B5" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="E5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:10" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="1" t="s">
+      <c r="B6" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="E6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" s="9"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:10" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="B7" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-    </row>
-    <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="1" t="s">
+      <c r="C7" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="E7" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G7" s="9"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="B8" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-    </row>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="1" t="s">
+      <c r="D8" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="E8" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:10" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="B9" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-    </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="1" t="s">
+      <c r="E9" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G9" s="9"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:10" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A10" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B10" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="E10" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="9"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:10" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A11" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="B11" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-    </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="1" t="s">
+      <c r="D11" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="E11" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="1:10" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A12" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="B12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:10" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A13" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="1:10" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A14" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A15" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="1:10" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A16" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G16" s="9"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:10" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A17" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" s="9"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10" ht="14.25" customHeight="1"/>
+    <row r="19" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A20" s="2"/>
+    </row>
+    <row r="21" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A21" s="2"/>
+    </row>
+    <row r="22" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A22" s="2"/>
+    </row>
+    <row r="23" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A23" s="2"/>
+      <c r="B23" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A24" s="2"/>
+    </row>
+    <row r="25" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A25" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A26" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A27" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A28" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A29" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A31" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A32" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A34" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A35" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="1" t="s">
+      <c r="B35" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A36" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="D36" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A37" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="B37" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A38" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="1" t="s">
+      <c r="B38" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A39" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="B39" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A40" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-    </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="1" t="s">
+      <c r="B40" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A41" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-    </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-    </row>
-    <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-    </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-    </row>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-    </row>
-    <row r="18" ht="14.25" customHeight="1"/>
-    <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-    </row>
-    <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="6"/>
-    </row>
-    <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="6"/>
-    </row>
-    <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="6"/>
-    </row>
-    <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="6"/>
-    </row>
-    <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D34" s="9" t="s">
+      <c r="B41" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E34" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" s="9" t="s">
+      <c r="C41" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C35" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D35" s="9" t="s">
+      <c r="D41" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E35" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" ht="14.25" customHeight="1"/>
-    <row r="43" ht="14.25" customHeight="1"/>
-    <row r="44" ht="14.25" customHeight="1"/>
-    <row r="45" ht="14.25" customHeight="1"/>
-    <row r="46" ht="14.25" customHeight="1"/>
-    <row r="47" ht="14.25" customHeight="1"/>
-    <row r="48" ht="14.25" customHeight="1"/>
+      <c r="E41" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="43" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="44" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="45" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="46" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="47" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="48" spans="1:5" ht="14.25" customHeight="1"/>
     <row r="49" ht="14.25" customHeight="1"/>
     <row r="50" ht="14.25" customHeight="1"/>
     <row r="51" ht="14.25" customHeight="1"/>
@@ -2259,9 +2455,7 @@
     <row r="999" ht="14.25" customHeight="1"/>
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>